--- a/notebooks/jesuitas-entrada-full.xlsx
+++ b/notebooks/jesuitas-entrada-full.xlsx
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2275,7 +2275,11 @@
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>extra_info: {"value": {"comment": "Segundo Dominguez &amp; O Neil, V.III,p.2961"}}</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -12201,7 +12205,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Louis Buglio 1688"}}</t>
+          <t>extra_info: {"value": {"comment": "Segundo Louis Buglio 1688"}}</t>
         </is>
       </c>
     </row>
@@ -23666,7 +23670,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -23691,7 +23695,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "ou 15600325"}}</t>
+          <t>extra_info: {"date": {"comment": "ou 15600325"}, "value": {"comment": "Domingues &amp; O Neil, IV: 2645"}}</t>
         </is>
       </c>
     </row>

--- a/notebooks/jesuitas-entrada-full.xlsx
+++ b/notebooks/jesuitas-entrada-full.xlsx
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goa, Índia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3158,7 +3158,7 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1171"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q1171", "original": "Goa, \u00cdndia"}}</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "Em Coimbra no ano de 1582 segundo a Carta Annua de 1623."}}</t>
+          <t>Corrigido: local de entrada extra_info: {"value": {"comment": "Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA"}}</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Itália (Luca)</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">

--- a/notebooks/jesuitas-entrada-full.xlsx
+++ b/notebooks/jesuitas-entrada-full.xlsx
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lisboa, Arroios</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "entra para a China"}, "value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"date": {"comment": "entra para a China"}, "value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lisboa, Arroios</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"value": {"comment": "[Arroios Rodrigues, Hist\u00f3ria Da Companhia de Jesus Na Assist\u00eancia de Portugal v4:167] @wikidata:Q597"}}</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2656"}}</t>
+          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Messina, Sicília</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Messina, Sicília</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q13666"}}</t>
+          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q13666"}}</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"value": {"comment": "[Arroios Rodrigues, Hist\u00f3ria Da Companhia de Jesus Na Assist\u00eancia de Portugal v4:167] @wikidata:Q597"}}</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Lisboa, Arroios</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Brno, República Checa</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14960"}}</t>
+          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Messina, Sicília</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Montmartre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Será que vale mesmo a pena chamar-lhe entrada? extra_info: {"value": {"comment": "@wikidata:Q186115"}}</t>
+          <t>Será que vale mesmo a pena chamar-lhe entrada? extra_info: {"value": {"comment": "(Montmartre) @wikidata:Q186115"}}</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Montmartre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11476,7 +11476,7 @@
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Será que vale mesmo a pena chamar-lhe entrada? extra_info: {"value": {"comment": "@wikidata:Q186115"}}</t>
+          <t>Será que vale mesmo a pena chamar-lhe entrada? extra_info: {"value": {"comment": "(Montmartre) @wikidata:Q186115"}}</t>
         </is>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Brno, República Checa</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "ou 16840918"}, "value": {"comment": "@wikidata:Q14960"}}</t>
+          <t>extra_info: {"date": {"comment": "ou 16840918"}, "value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -12294,12 +12294,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -13739,7 +13739,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2656"}}</t>
+          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q111218"}}</t>
+          <t>"https://roccadellacultura.it/opere-e-contenuti/la-spezieria-dei-gesuiti-di-novellara" extra_info: {"value": {"comment": "@wikidata:Q111218"}}</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -13977,12 +13977,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q2656"}}</t>
+          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14348,12 +14348,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "j\u00e1 padre"}, "value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"date": {"comment": "j\u00e1 padre"}, "value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Brno, República Checa</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -20515,7 +20515,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14960"}}</t>
+          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Lisboa, Arroios</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:@wikidata:Q15041623"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:@wikidata:Q15041623", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Brno, República Checa</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14960"}}</t>
+          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>destinado à China em 1785, viagem abortada extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>destinado à China em 1785, viagem abortada extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -23039,7 +23039,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -23064,7 +23064,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>antes entrara na ordem de Malta em 16120518 diz Dehergne «La première entrée — avant « l'âge de raison » — est une « E. de dévotion », désirée par ses parents, qui consacrent leur fils au Seigneur et le revêtent des habits de l'Ordre, les Chevaliers de Malte.» extra_info: {"value": {"comment": "@wikidata:Q2656"}}</t>
+          <t>antes entrara na ordem de Malta em 16120518 diz Dehergne «La première entrée — avant « l'âge de raison » — est une « E. de dévotion », désirée par ses parents, qui consacrent leur fils au Seigneur et le revêtent des habits de l'Ordre, les Chevaliers de Malte.» extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q2656"}}</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Caltavuturo, Palermo, Sicília</t>
+          <t>Caltavuturo, Palermo</t>
         </is>
       </c>
       <c r="G669" t="inlineStr"/>
@@ -27597,7 +27597,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -27617,12 +27617,12 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Messina, Sicília</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q13666"}}</t>
+          <t>extra_info: {"value": {"comment": "[Sic\u00edlia] @wikidata:Q13666"}}</t>
         </is>
       </c>
     </row>
@@ -30318,7 +30318,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Viena, Áustria</t>
+          <t>Viena</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -30343,7 +30343,7 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q1741"}}</t>
+          <t>extra_info: {"value": {"comment": "[\u00c1ustria] @wikidata:Q1741"}}</t>
         </is>
       </c>
     </row>
@@ -31844,7 +31844,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>Fraça</t>
+          <t>França</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>Fraça</t>
+          <t>França</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
@@ -32224,7 +32224,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Lisboa, Arroios</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -32500,7 +32500,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Shiuchow, Chao-tcheou fou</t>
+          <t>Shiuchow</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -32525,7 +32525,7 @@
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}}</t>
+          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}, "value": {"original": "Chao-tcheou fou"}}</t>
         </is>
       </c>
     </row>
@@ -32537,7 +32537,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Shiuchow, Chao-tcheou fou</t>
+          <t>Shiuchow</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -32554,7 +32554,7 @@
       <c r="F918" t="inlineStr"/>
       <c r="G918" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}}</t>
+          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}, "value": {"original": "Chao-tcheou fou"}}</t>
         </is>
       </c>
     </row>
@@ -33801,7 +33801,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>Novellario</t>
+          <t>Novellara</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -33826,7 +33826,7 @@
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "ILOC"}}</t>
+          <t>extra_info: {"value": {"comment": "[Assume-se Novellara, nascido a 40km] @wikidata:Q111218", "original": "Novellario"}}</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Lisboa, Arroios</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "destinado \u00e0 China"}, "value": {"comment": "@wikidata:Q597"}}</t>
+          <t>extra_info: {"date": {"comment": "destinado \u00e0 China"}, "value": {"comment": "@wikidata:Q597", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -34175,7 +34175,7 @@
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>Palermo, Sicília</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G964" t="inlineStr"/>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>Brno, República Checa</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14960"}}</t>
+          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Brno, República Checa</t>
+          <t>Brno</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -34283,7 +34283,7 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:Q14960"}}</t>
+          <t>extra_info: {"value": {"comment": "[Rep\u00fablica Checa] @wikidata:Q14960"}}</t>
         </is>
       </c>
     </row>

--- a/notebooks/jesuitas-entrada-full.xlsx
+++ b/notebooks/jesuitas-entrada-full.xlsx
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Segundo Louis Buglio 1688", "original": "Coimbra"}}</t>
+          <t>extra_info: {"value": {"comment": "Segundo Louis Buglio 1688", "original": "?"}}</t>
         </is>
       </c>
     </row>

--- a/notebooks/jesuitas-entrada-full.xlsx
+++ b/notebooks/jesuitas-entrada-full.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Landsberg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[JRC Entrou em Landsberg, Alemanha segundo "http://www.conimbricenses.org/encyclopedia/aigenler-adam/"]</t>
+          <t>[JRC Entrou em Landsberg, Alemanha segundo "http://www.conimbricenses.org/encyclopedia/aigenler-adam/"] extra_info: {"value": {"comment": "Golvers, 2019 @wikidata:Q39793", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[Brockey diz "educated at the College of Coimbra" cap.6 nota 95, citando a carta ânua de 1656, Ajuda, 49-V.14:62v] extra_info: {"value": {"comment": "Brockey, cap.6 n.95", "original": "?"}}</t>
+          <t>[Brockey diz "educated at the College of Coimbra" cap.6 nota 95, citando a carta ânua de 1656, Ajuda, 49-V.14:62v] extra_info: {"value": {"comment": "@wikidata:Q45412 Brockey, cap.6 n.95", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Segundo Dominguez &amp; O Neil, V.III,p.2961. Franco Imagem...Coimbra,II,4,c.36,p.575", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Segundo Dominguez &amp; O Neil, V.III,p.2961. Franco Imagem...Coimbra,II,4,c.36,p.575", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Franco, 1717, p. 375, Sweet, 20216, p.27@wikidata:Q45412"}}</t>
+          <t>extra_info: {"value": {"comment": "Franco, 1717, p. 375, Sweet, 20216, p.27 @wikidata:Q45412"}}</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "ou 16090502"}, "value": {"comment": "(Franco, 1719, t.II, p. 612)", "original": "?"}}</t>
+          <t>extra_info: {"date": {"comment": "ou 16090502"}, "value": {"comment": "@wikidata:Q45412 (Franco, 1719, t.II, p. 612)", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "\"\"\"Franco, Imagem...Coimbra, v.2 p.616; Barbosa Machado, v.3\"\"\"", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 \"\"\"Franco, Imagem...Coimbra, v.2 p.616; Barbosa Machado, v.3\"\"\"", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Segundo Louis Buglio 1688", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Segundo Louis Buglio 1688", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "MMHM:p.8"}, "value": {"comment": "[Adicionado a partir de Franco, Imagem...Coimbra, II, 522", "original": "?"}}</t>
+          <t>extra_info: {"date": {"comment": "MMHM:p.8"}, "value": {"comment": "[Adicionado a partir de Franco, Imagem...Coimbra, II, 522] @wikidata:Q45412", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "no noviciado"}, "value": {"original": "(Chao-tcheou)"}}</t>
+          <t>extra_info: {"date": {"comment": "no noviciado"}, "value": {"comment": "@wikidata:Q1346617", "original": "(Chao-tcheou)"}}</t>
         </is>
       </c>
     </row>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Corrigido: local de entrada extra_info: {"value": {"comment": "Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA", "original": "?"}}</t>
+          <t>Corrigido: local de entrada extra_info: {"value": {"comment": "@wikidata:Q45412 Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -21139,7 +21139,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "ou 15600325 ou Coimbra, 25-03-1560 MMHM"}, "value": {"comment": "Domingues &amp; O Neil, IV: 2645. MMHM:p.226", "original": "?"}}</t>
+          <t>extra_info: {"date": {"comment": "ou 15600325 ou Coimbra, 25-03-1560 MMHM"}, "value": {"comment": "@wikidata:Q45412 Domingues &amp; O Neil, IV: 2645. MMHM:p.226", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Segungo Dominguez, J. M., &amp; O\u2019Neill, C. (2001) II, 1113", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Segungo Dominguez, J. M., &amp; O\u2019Neill, C. (2001) II, 1113", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -22980,7 +22980,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Schutte, Monumenta historica japoniae I.,p.1180", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Schutte, Monumenta historica japoniae I.,p.1180", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "MMHM:p.94 (ARSI Japsin 35 13)", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 MMHM:p.94 (ARSI Japsin 35 13)", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -24219,7 +24219,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "MMHM:p.203 (Matias d'Amaia), Schutte, Monumenta historica japoniae I.1234", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 MMHM:p.203 (Matias d'Amaia), Schutte, Monumenta historica japoniae I.1234", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -28800,7 +28800,7 @@
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "MMHM:p.205 (Sebastian da Maia, da Maya, d'Amaya)", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 MMHM:p.205 (Sebastian da Maia, da Maya, d'Amaya)", "original": "?"}}</t>
         </is>
       </c>
     </row>
@@ -28944,7 +28944,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}, "value": {"original": "Chao-tcheou fou"}}</t>
+          <t>extra_info: {"date": {"comment": "fim do m\u00eas"}, "value": {"comment": "@wikidata: Q1346617", "original": "Chao-tcheou fou"}}</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "Dehergne n\u00e3o especifica local, Brockey estudos Filosofia e Teologia em Coimbra", "original": "?"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q45412 Dehergne n\u00e3o especifica local, Brockey estudos Filosofia e Teologia em Coimbra", "original": "?"}}</t>
         </is>
       </c>
     </row>

--- a/notebooks/jesuitas-entrada-full.xlsx
+++ b/notebooks/jesuitas-entrada-full.xlsx
@@ -12645,7 +12645,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12668,7 +12668,11 @@
           <t>Vila Real, diocese de Braga</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>extra_info: {"value": {"original": "? Segundo Sch\u00fctte, p.1174"}}</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
@@ -18554,7 +18558,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>extra_info: {"value": {"comment": "@wikidata:@wikidata:Q15041623", "original": "Lisboa, Arroios"}}</t>
+          <t>extra_info: {"value": {"comment": "@wikidata:Q15041623", "original": "Lisboa, Arroios"}}</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28857,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -28876,7 +28880,11 @@
           <t>Castro Daire, diocese de Lamego</t>
         </is>
       </c>
-      <c r="G806" t="inlineStr"/>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>extra_info: {"value": {"comment": "([Sch\u00fctte, 1975, p. 1321] Sebasti\u00e3o Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591", "original": "?"}}</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="1" t="inlineStr">
